--- a/StructureDefinition-ophthalmic-imaging-study.xlsx
+++ b/StructureDefinition-ophthalmic-imaging-study.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-01T17:43:23+00:00</t>
+    <t>2026-09-11T00:16:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-ophthalmic-imaging-study.xlsx
+++ b/StructureDefinition-ophthalmic-imaging-study.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-11T00:16:12+00:00</t>
+    <t>2026-10-19T22:17:00-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1816,17 +1816,17 @@
   <dimension ref="A1:AO62"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.67578125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="40.13671875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.98046875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.8828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.77734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.55078125" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="107.140625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="113.71875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1835,27 +1835,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="50.890625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="49.63671875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="74.78125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="32.90234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="50.9140625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="50.3203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="78.59765625" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="33.2734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.51953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.859375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="97.94921875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="89.92578125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.9609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="99.20703125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="90.34765625" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="29.45703125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="22.43359375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/StructureDefinition-ophthalmic-imaging-study.xlsx
+++ b/StructureDefinition-ophthalmic-imaging-study.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$57</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2312" uniqueCount="470">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2132" uniqueCount="442">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:17:00-03:00</t>
+    <t>2026-10-20T20:13:11-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,12 +87,11 @@
     <t>Description</t>
   </si>
   <si>
-    <t>An ophthalmic imaging study, such as OCT, retinography, or angiography.
-Always traceable back to the medical order that led to it via basedOn. Laterality is
-represented both through the native series.bodySite/series.laterality Coding fields (for
-standard DICOM/PACS compatibility) and through an additional extension referencing
-OcularBodyStructure (for structured cross-resource navigation, consistent with the rest of
-this guide).</t>
+    <t>An ophthalmic imaging study, such as OCT, retinography, or angiography.
+Always traceable back to the medical order that led to it via basedOn. Laterality is
+represented through the native series.bodySite/series.laterality Coding fields (for
+standard DICOM/PACS compatibility); the core bodySite extension is not allowed on
+ImagingStudy.series in FHIR R4.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1011,95 +1010,10 @@
     <t>ImagingStudy.series.extension</t>
   </si>
   <si>
-    <t>Extension</t>
-  </si>
-  <si>
-    <t>An Extension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>open</t>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension:bodySiteEye</t>
-  </si>
-  <si>
-    <t>bodySiteEye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {bodySite}
-</t>
-  </si>
-  <si>
-    <t>Structured reference to the same OcularBodyStructure instance used elsewhere for this patient/encounter</t>
-  </si>
-  <si>
-    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension:bodySiteEye.id</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension.id</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension:bodySiteEye.extension</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension.extension</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension:bodySiteEye.url</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension.url</t>
-  </si>
-  <si>
-    <t>identifies the meaning of the extension</t>
-  </si>
-  <si>
-    <t>Source of the definition for the extension code - a logical name or a URL.</t>
-  </si>
-  <si>
-    <t>The definition may point directly to a computable or human-readable definition of the extensibility codes, or it may be a logical URI as declared in some other specification. The definition SHALL be a URI for the Structure Definition defining the extension.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodySite</t>
-  </si>
-  <si>
-    <t>Extension.url</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension:bodySiteEye.value[x]</t>
-  </si>
-  <si>
-    <t>ImagingStudy.series.extension.value[x]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(https://YasniiSS.github.io/fhir4eyes/StructureDefinition/ocular-body-structure)
-</t>
-  </si>
-  <si>
-    <t>Value of extension</t>
-  </si>
-  <si>
-    <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
-  </si>
-  <si>
-    <t>Extension.value[x]</t>
   </si>
   <si>
     <t>ImagingStudy.series.modifierExtension</t>
@@ -1338,9 +1252,6 @@
   </si>
   <si>
     <t>ImagingStudy.series.performer.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>ImagingStudy.series.performer.modifierExtension</t>
@@ -1813,12 +1724,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO62"/>
+  <dimension ref="A1:AO57"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.98046875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="40.8828125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="40.8828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="10.77734375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="9.984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.8125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1844,7 +1755,7 @@
     <col min="26" max="26" width="78.59765625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="33.2734375" customWidth="true" bestFit="true" hidden="true"/>
@@ -5476,7 +5387,7 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
@@ -5498,12 +5409,14 @@
         <v>136</v>
       </c>
       <c r="L32" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M32" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="N32" s="2"/>
+      <c r="N32" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>79</v>
@@ -5540,17 +5453,19 @@
         <v>79</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AC32" s="2"/>
+        <v>79</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>79</v>
+      </c>
       <c r="AD32" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5568,7 +5483,7 @@
         <v>79</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>79</v>
+        <v>314</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>79</v>
@@ -5580,46 +5495,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>322</v>
-      </c>
+        <v>318</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="I33" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I33" t="s" s="2">
-        <v>79</v>
-      </c>
       <c r="J33" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>323</v>
+        <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N33" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O33" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P33" t="s" s="2">
         <v>79</v>
       </c>
@@ -5667,7 +5584,7 @@
         <v>79</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5676,7 +5593,7 @@
         <v>81</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>326</v>
+        <v>79</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>141</v>
@@ -5685,7 +5602,7 @@
         <v>79</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>79</v>
+        <v>133</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>79</v>
@@ -5697,44 +5614,48 @@
         <v>79</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>328</v>
+        <v>323</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>79</v>
+        <v>324</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>90</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>300</v>
+        <v>92</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>311</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="O34" t="s" s="2">
+        <v>328</v>
+      </c>
       <c r="P34" t="s" s="2">
         <v>79</v>
       </c>
@@ -5746,7 +5667,7 @@
         <v>79</v>
       </c>
       <c r="T34" t="s" s="2">
-        <v>79</v>
+        <v>329</v>
       </c>
       <c r="U34" t="s" s="2">
         <v>79</v>
@@ -5782,10 +5703,10 @@
         <v>79</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>90</v>
@@ -5794,16 +5715,16 @@
         <v>79</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>79</v>
+        <v>331</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>79</v>
@@ -5814,21 +5735,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>79</v>
+        <v>333</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>79</v>
@@ -5837,16 +5758,16 @@
         <v>79</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>136</v>
+        <v>239</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5861,7 +5782,7 @@
         <v>79</v>
       </c>
       <c r="T35" t="s" s="2">
-        <v>79</v>
+        <v>336</v>
       </c>
       <c r="U35" t="s" s="2">
         <v>79</v>
@@ -5885,40 +5806,40 @@
         <v>79</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>318</v>
+        <v>79</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>331</v>
+        <v>79</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>319</v>
+        <v>79</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK35" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>79</v>
+        <v>337</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>79</v>
+        <v>338</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>79</v>
@@ -5927,16 +5848,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>79</v>
+        <v>340</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5946,33 +5867,31 @@
         <v>90</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>104</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>337</v>
+        <v>79</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>79</v>
@@ -5990,13 +5909,13 @@
         <v>79</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>79</v>
@@ -6014,7 +5933,7 @@
         <v>79</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>90</v>
@@ -6026,16 +5945,16 @@
         <v>79</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK36" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>133</v>
+        <v>177</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>79</v>
+        <v>343</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>79</v>
@@ -6046,18 +5965,18 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
-        <v>79</v>
+        <v>345</v>
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>90</v>
@@ -6069,16 +5988,16 @@
         <v>79</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>341</v>
+        <v>300</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -6093,7 +6012,7 @@
         <v>79</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>79</v>
+        <v>348</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>79</v>
@@ -6147,10 +6066,10 @@
         <v>79</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>133</v>
+        <v>303</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>79</v>
+        <v>349</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>79</v>
@@ -6161,46 +6080,42 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I38" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J38" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>136</v>
+        <v>239</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>145</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>79</v>
       </c>
@@ -6248,28 +6163,28 @@
         <v>79</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>133</v>
+        <v>248</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>79</v>
+        <v>354</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>79</v>
@@ -6278,26 +6193,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>351</v>
+        <v>79</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>79</v>
@@ -6306,19 +6221,19 @@
         <v>91</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>92</v>
+        <v>231</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>79</v>
@@ -6331,7 +6246,7 @@
         <v>79</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>356</v>
+        <v>79</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>79</v>
@@ -6367,13 +6282,13 @@
         <v>79</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>79</v>
@@ -6385,10 +6300,10 @@
         <v>79</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>357</v>
+        <v>236</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>358</v>
+        <v>79</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>79</v>
@@ -6397,16 +6312,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6416,7 +6331,7 @@
         <v>90</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>79</v>
@@ -6425,13 +6340,13 @@
         <v>91</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>239</v>
+        <v>171</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6446,7 +6361,7 @@
         <v>79</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>363</v>
+        <v>79</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>79</v>
@@ -6458,13 +6373,13 @@
         <v>79</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>79</v>
+        <v>278</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>79</v>
+        <v>364</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>79</v>
+        <v>365</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>79</v>
@@ -6482,7 +6397,7 @@
         <v>79</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6500,10 +6415,10 @@
         <v>79</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>79</v>
@@ -6514,18 +6429,18 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>367</v>
+        <v>79</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>90</v>
@@ -6543,10 +6458,10 @@
         <v>171</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6573,13 +6488,13 @@
         <v>79</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>174</v>
+        <v>278</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>175</v>
+        <v>371</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>176</v>
+        <v>372</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>79</v>
@@ -6597,10 +6512,10 @@
         <v>79</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>90</v>
@@ -6615,10 +6530,10 @@
         <v>79</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>177</v>
+        <v>366</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>79</v>
@@ -6629,21 +6544,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>372</v>
+        <v>79</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>79</v>
@@ -6655,13 +6570,13 @@
         <v>91</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>300</v>
+        <v>375</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6676,7 +6591,7 @@
         <v>79</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>375</v>
+        <v>79</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>79</v>
@@ -6712,13 +6627,13 @@
         <v>79</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>79</v>
@@ -6730,10 +6645,10 @@
         <v>79</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>303</v>
+        <v>378</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>79</v>
@@ -6744,14 +6659,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>378</v>
+        <v>79</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6770,13 +6685,13 @@
         <v>91</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>239</v>
+        <v>199</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6827,7 +6742,7 @@
         <v>79</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -6845,10 +6760,10 @@
         <v>79</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>248</v>
+        <v>204</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>79</v>
@@ -6859,14 +6774,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>79</v>
+        <v>385</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -6885,19 +6800,19 @@
         <v>91</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>231</v>
+        <v>306</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>79</v>
@@ -6946,7 +6861,7 @@
         <v>79</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -6961,13 +6876,13 @@
         <v>102</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>79</v>
+        <v>390</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>79</v>
+        <v>391</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>79</v>
@@ -6976,16 +6891,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>388</v>
+        <v>79</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
@@ -6995,22 +6910,22 @@
         <v>90</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>171</v>
+        <v>300</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>389</v>
+        <v>311</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>390</v>
+        <v>312</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7037,13 +6952,13 @@
         <v>79</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>391</v>
+        <v>79</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>392</v>
+        <v>79</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>79</v>
@@ -7061,7 +6976,7 @@
         <v>79</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>387</v>
+        <v>313</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7073,61 +6988,63 @@
         <v>79</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL45" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AO45" t="s" s="2">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
         <v>393</v>
       </c>
-      <c r="AM45" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>395</v>
-      </c>
       <c r="B46" t="s" s="2">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>79</v>
+        <v>135</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>171</v>
+        <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>396</v>
+        <v>137</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="N46" s="2"/>
+        <v>316</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>79</v>
@@ -7152,13 +7069,13 @@
         <v>79</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>278</v>
+        <v>79</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>398</v>
+        <v>79</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>399</v>
+        <v>79</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>79</v>
@@ -7176,28 +7093,28 @@
         <v>79</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>395</v>
+        <v>317</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>393</v>
+        <v>314</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>400</v>
+        <v>79</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>79</v>
@@ -7208,14 +7125,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7228,22 +7145,26 @@
         <v>79</v>
       </c>
       <c r="I47" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J47" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>402</v>
+        <v>136</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>403</v>
+        <v>320</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>139</v>
+      </c>
+      <c r="O47" t="s" s="2">
+        <v>145</v>
+      </c>
       <c r="P47" t="s" s="2">
         <v>79</v>
       </c>
@@ -7291,7 +7212,7 @@
         <v>79</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>401</v>
+        <v>322</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7303,16 +7224,16 @@
         <v>79</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>405</v>
+        <v>133</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>406</v>
+        <v>79</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>79</v>
@@ -7323,10 +7244,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7349,16 +7270,18 @@
         <v>91</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>199</v>
+        <v>259</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>408</v>
+        <v>396</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="N48" s="2"/>
-      <c r="O48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>398</v>
+      </c>
       <c r="P48" t="s" s="2">
         <v>79</v>
       </c>
@@ -7382,13 +7305,13 @@
         <v>79</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>79</v>
+        <v>399</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>79</v>
+        <v>400</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>79</v>
@@ -7406,7 +7329,7 @@
         <v>79</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7424,10 +7347,10 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>410</v>
+        <v>79</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>79</v>
@@ -7438,21 +7361,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>412</v>
+        <v>79</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>79</v>
@@ -7464,20 +7387,16 @@
         <v>91</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>306</v>
+        <v>402</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>413</v>
+        <v>386</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>416</v>
-      </c>
+        <v>403</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>79</v>
       </c>
@@ -7525,13 +7444,13 @@
         <v>79</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="AG49" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>79</v>
@@ -7540,27 +7459,27 @@
         <v>102</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>417</v>
+        <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>227</v>
+        <v>404</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>418</v>
+        <v>79</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>79</v>
+        <v>405</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>79</v>
+        <v>406</v>
       </c>
     </row>
-    <row r="50" hidden="true">
+    <row r="50">
       <c r="A50" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7571,10 +7490,10 @@
         <v>80</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H50" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I50" t="s" s="2">
         <v>79</v>
@@ -7583,13 +7502,13 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>311</v>
+        <v>408</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>312</v>
+        <v>409</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7640,25 +7559,25 @@
         <v>79</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>313</v>
+        <v>407</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>314</v>
+        <v>410</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7672,21 +7591,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>79</v>
@@ -7698,17 +7617,15 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>136</v>
+        <v>300</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>137</v>
+        <v>311</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>421</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>139</v>
-      </c>
+        <v>312</v>
+      </c>
+      <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>79</v>
@@ -7757,19 +7674,19 @@
         <v>79</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>141</v>
+        <v>79</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>79</v>
@@ -7789,14 +7706,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>346</v>
+        <v>135</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7809,26 +7726,24 @@
         <v>79</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
         <v>136</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>347</v>
+        <v>137</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>348</v>
+        <v>316</v>
       </c>
       <c r="N52" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="O52" t="s" s="2">
-        <v>145</v>
-      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>79</v>
       </c>
@@ -7876,7 +7791,7 @@
         <v>79</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>349</v>
+        <v>317</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -7894,7 +7809,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>133</v>
+        <v>314</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7908,43 +7823,45 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
-        <v>79</v>
+        <v>319</v>
       </c>
       <c r="E53" s="2"/>
       <c r="F53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="I53" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="J53" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>424</v>
+        <v>320</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>139</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>426</v>
+        <v>145</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>79</v>
@@ -7969,13 +7886,13 @@
         <v>79</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>174</v>
+        <v>79</v>
       </c>
       <c r="Y53" t="s" s="2">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="Z53" t="s" s="2">
-        <v>428</v>
+        <v>79</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>79</v>
@@ -7993,25 +7910,25 @@
         <v>79</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>423</v>
+        <v>322</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ53" t="s" s="2">
-        <v>102</v>
+        <v>141</v>
       </c>
       <c r="AK53" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>227</v>
+        <v>133</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -8023,16 +7940,16 @@
         <v>79</v>
       </c>
     </row>
-    <row r="54" hidden="true">
+    <row r="54">
       <c r="A54" t="s" s="2">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>79</v>
+        <v>415</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8042,25 +7959,29 @@
         <v>90</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>79</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>430</v>
+        <v>92</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" s="2"/>
+        <v>417</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="O54" t="s" s="2">
+        <v>419</v>
+      </c>
       <c r="P54" t="s" s="2">
         <v>79</v>
       </c>
@@ -8072,7 +7993,7 @@
         <v>79</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>79</v>
+        <v>420</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>79</v>
@@ -8108,7 +8029,7 @@
         <v>79</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>90</v>
@@ -8126,35 +8047,35 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>432</v>
+        <v>330</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>79</v>
+        <v>421</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>433</v>
+        <v>79</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>434</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>79</v>
+        <v>423</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>91</v>
@@ -8166,13 +8087,13 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>306</v>
+        <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>436</v>
+        <v>424</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>437</v>
+        <v>425</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8199,13 +8120,13 @@
         <v>79</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>79</v>
+        <v>174</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>79</v>
+        <v>426</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>79</v>
+        <v>427</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>79</v>
@@ -8223,13 +8144,13 @@
         <v>79</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="AG55" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>79</v>
@@ -8241,10 +8162,10 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>79</v>
+        <v>429</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>79</v>
@@ -8255,14 +8176,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>439</v>
+        <v>430</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>79</v>
+        <v>431</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8281,13 +8202,13 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>300</v>
+        <v>239</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>311</v>
+        <v>432</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>312</v>
+        <v>433</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8302,7 +8223,7 @@
         <v>79</v>
       </c>
       <c r="T56" t="s" s="2">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="U56" t="s" s="2">
         <v>79</v>
@@ -8338,7 +8259,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>313</v>
+        <v>430</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8350,16 +8271,16 @@
         <v>79</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>314</v>
+        <v>434</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>79</v>
+        <v>435</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>79</v>
@@ -8368,26 +8289,26 @@
         <v>79</v>
       </c>
     </row>
-    <row r="57" hidden="true">
+    <row r="57">
       <c r="A57" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>79</v>
@@ -8396,16 +8317,16 @@
         <v>79</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>136</v>
+        <v>300</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>137</v>
+        <v>437</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>421</v>
+        <v>438</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>139</v>
+        <v>439</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -8455,623 +8376,38 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>320</v>
+        <v>436</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="AK57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>314</v>
+        <v>440</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>79</v>
+        <v>441</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>139</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>145</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>141</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" s="2"/>
-      <c r="P60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>460</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>461</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
-      <c r="P61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>462</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>463</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO61" t="s" s="2">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="C62" s="2"/>
-      <c r="D62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="E62" s="2"/>
-      <c r="F62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H62" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="I62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="J62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="K62" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="L62" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="M62" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>467</v>
-      </c>
-      <c r="O62" s="2"/>
-      <c r="P62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="S62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="T62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="U62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="V62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="W62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="X62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Y62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="Z62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AA62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF62" t="s" s="2">
-        <v>464</v>
-      </c>
-      <c r="AG62" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH62" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AJ62" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL62" t="s" s="2">
-        <v>468</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AO62" t="s" s="2">
         <v>79</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO62">
+  <autoFilter ref="A1:AO57">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9081,7 +8417,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI61">
+  <conditionalFormatting sqref="A2:AI56">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
